--- a/product/generated/polysync-unit-economics.xlsx
+++ b/product/generated/polysync-unit-economics.xlsx
@@ -10,43 +10,50 @@
   <sheets>
     <sheet name="Read me" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Drivers" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Escalation" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Amber outcomes" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Unit economics" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Penetration" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Sources" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="amberDaysPerAthleteMonth" vbProcedure="false">Drivers!$C$2</definedName>
-    <definedName function="false" hidden="false" name="arrTargetUsd" vbProcedure="false">Drivers!$C$24</definedName>
-    <definedName function="false" hidden="false" name="athletesPerClub" vbProcedure="false">Drivers!$C$21</definedName>
-    <definedName function="false" hidden="false" name="coachLoading" vbProcedure="false">Drivers!$C$10</definedName>
-    <definedName function="false" hidden="false" name="coachProgrammingHoursPerWeek" vbProcedure="false">Drivers!$C$12</definedName>
-    <definedName function="false" hidden="false" name="esc_flexible" vbProcedure="false">Escalation!$D$14</definedName>
-    <definedName function="false" hidden="false" name="esc_rigid" vbProcedure="false">Escalation!$D$16</definedName>
-    <definedName function="false" hidden="false" name="esc_standard" vbProcedure="false">Escalation!$D$15</definedName>
-    <definedName function="false" hidden="false" name="fxAedPerUsd" vbProcedure="false">Drivers!$C$28</definedName>
+    <definedName function="false" hidden="false" name="arrTargetUsd" vbProcedure="false">Drivers!$C$25</definedName>
+    <definedName function="false" hidden="false" name="athletesPerClub" vbProcedure="false">Drivers!$C$22</definedName>
+    <definedName function="false" hidden="false" name="coachLoading" vbProcedure="false">Drivers!$C$11</definedName>
+    <definedName function="false" hidden="false" name="coachProgrammingHoursPerWeek" vbProcedure="false">Drivers!$C$13</definedName>
+    <definedName function="false" hidden="false" name="down_flexible" vbProcedure="false">'Amber outcomes'!$D$14</definedName>
+    <definedName function="false" hidden="false" name="down_rigid" vbProcedure="false">'Amber outcomes'!$D$16</definedName>
+    <definedName function="false" hidden="false" name="down_standard" vbProcedure="false">'Amber outcomes'!$D$15</definedName>
+    <definedName function="false" hidden="false" name="esc_flexible" vbProcedure="false">'Amber outcomes'!$E$14</definedName>
+    <definedName function="false" hidden="false" name="esc_rigid" vbProcedure="false">'Amber outcomes'!$E$16</definedName>
+    <definedName function="false" hidden="false" name="esc_standard" vbProcedure="false">'Amber outcomes'!$E$15</definedName>
+    <definedName function="false" hidden="false" name="fxAedPerUsd" vbProcedure="false">Drivers!$C$29</definedName>
     <definedName function="false" hidden="false" name="hardShareOnAmber" vbProcedure="false">Drivers!$C$3</definedName>
-    <definedName function="false" hidden="false" name="hyroxGyms" vbProcedure="false">Drivers!$C$22</definedName>
-    <definedName function="false" hidden="false" name="infraPerAthleteMonthUsd" vbProcedure="false">Drivers!$C$18</definedName>
-    <definedName function="false" hidden="false" name="llmCallsPerAthleteMonth" vbProcedure="false">Drivers!$C$15</definedName>
+    <definedName function="false" hidden="false" name="hyroxGyms" vbProcedure="false">Drivers!$C$23</definedName>
+    <definedName function="false" hidden="false" name="infraPerAthleteMonthUsd" vbProcedure="false">Drivers!$C$19</definedName>
+    <definedName function="false" hidden="false" name="kept_flexible" vbProcedure="false">'Amber outcomes'!$C$14</definedName>
+    <definedName function="false" hidden="false" name="kept_rigid" vbProcedure="false">'Amber outcomes'!$C$16</definedName>
+    <definedName function="false" hidden="false" name="kept_standard" vbProcedure="false">'Amber outcomes'!$C$15</definedName>
+    <definedName function="false" hidden="false" name="llmCallsPerAthleteMonth" vbProcedure="false">Drivers!$C$16</definedName>
     <definedName function="false" hidden="false" name="llmProposalsPerAthleteMonth" vbProcedure="false">Drivers!$C$5</definedName>
-    <definedName function="false" hidden="false" name="llmTokensInPerProposal" vbProcedure="false">Drivers!$C$13</definedName>
-    <definedName function="false" hidden="false" name="llmTokensOutPerProposal" vbProcedure="false">Drivers!$C$14</definedName>
-    <definedName function="false" hidden="false" name="manualMinutesPerAthleteWeek" vbProcedure="false">Drivers!$C$9</definedName>
-    <definedName function="false" hidden="false" name="minutesPerEscalation" vbProcedure="false">Drivers!$C$7</definedName>
+    <definedName function="false" hidden="false" name="llmTokensInPerProposal" vbProcedure="false">Drivers!$C$14</definedName>
+    <definedName function="false" hidden="false" name="llmTokensOutPerProposal" vbProcedure="false">Drivers!$C$15</definedName>
+    <definedName function="false" hidden="false" name="manualMinutesPerAthleteWeek" vbProcedure="false">Drivers!$C$10</definedName>
+    <definedName function="false" hidden="false" name="minutesPerEscalation" vbProcedure="false">Drivers!$C$8</definedName>
+    <definedName function="false" hidden="false" name="minutesPerLostSession" vbProcedure="false">Drivers!$C$7</definedName>
     <definedName function="false" hidden="false" name="painFlagsPerAthleteMonth" vbProcedure="false">Drivers!$C$4</definedName>
-    <definedName function="false" hidden="false" name="paymentFeeRate" vbProcedure="false">Drivers!$C$20</definedName>
-    <definedName function="false" hidden="false" name="priceInPer1M" vbProcedure="false">Drivers!$C$16</definedName>
-    <definedName function="false" hidden="false" name="priceOutPer1M" vbProcedure="false">Drivers!$C$17</definedName>
-    <definedName function="false" hidden="false" name="pricePerAthleteMonthUsd" vbProcedure="false">Drivers!$C$19</definedName>
+    <definedName function="false" hidden="false" name="paymentFeeRate" vbProcedure="false">Drivers!$C$21</definedName>
+    <definedName function="false" hidden="false" name="priceInPer1M" vbProcedure="false">Drivers!$C$17</definedName>
+    <definedName function="false" hidden="false" name="priceOutPer1M" vbProcedure="false">Drivers!$C$18</definedName>
+    <definedName function="false" hidden="false" name="pricePerAthleteMonthUsd" vbProcedure="false">Drivers!$C$20</definedName>
     <definedName function="false" hidden="false" name="proposalRejectRate" vbProcedure="false">Drivers!$C$6</definedName>
-    <definedName function="false" hidden="false" name="specialistPremium" vbProcedure="false">Drivers!$C$11</definedName>
-    <definedName function="false" hidden="false" name="targetGrossMargin" vbProcedure="false">Drivers!$C$23</definedName>
-    <definedName function="false" hidden="false" name="triageMinutesPerAthleteWeek" vbProcedure="false">Drivers!$C$8</definedName>
-    <definedName function="false" hidden="false" name="uaeHoursPerMonth" vbProcedure="false">Drivers!$C$30</definedName>
-    <definedName function="false" hidden="false" name="uaeMonthlyWageAed" vbProcedure="false">Drivers!$C$29</definedName>
-    <definedName function="false" hidden="false" name="usHourlyWageUsd" vbProcedure="false">Drivers!$C$31</definedName>
-    <definedName function="false" hidden="false" name="weeksPerMonth" vbProcedure="false">Drivers!$C$27</definedName>
+    <definedName function="false" hidden="false" name="specialistPremium" vbProcedure="false">Drivers!$C$12</definedName>
+    <definedName function="false" hidden="false" name="targetGrossMargin" vbProcedure="false">Drivers!$C$24</definedName>
+    <definedName function="false" hidden="false" name="triageMinutesPerAthleteWeek" vbProcedure="false">Drivers!$C$9</definedName>
+    <definedName function="false" hidden="false" name="uaeHoursPerMonth" vbProcedure="false">Drivers!$C$31</definedName>
+    <definedName function="false" hidden="false" name="uaeMonthlyWageAed" vbProcedure="false">Drivers!$C$30</definedName>
+    <definedName function="false" hidden="false" name="usHourlyWageUsd" vbProcedure="false">Drivers!$C$32</definedName>
+    <definedName function="false" hidden="false" name="weeksPerMonth" vbProcedure="false">Drivers!$C$28</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -63,7 +70,7 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -71,7 +78,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Source: evals/results/hybrid-latest.json, amber_escalation_by_schedule (CI). Simulation of the engine's own rules.</t>
+          <t xml:space="preserve">Source: evals/results/hybrid-latest.json, amber_outcomes_by_schedule (CI). Simulation of the engine's own rules.</t>
         </r>
       </text>
     </comment>
@@ -80,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="281">
   <si>
     <t xml:space="preserve">PolySync unit economics</t>
   </si>
@@ -97,7 +104,7 @@
     <t xml:space="preserve">B2B2C (ADR-001): the club's coaches review escalations, so coach time is the club's cost. 'Managed break-even' is the price PolySync would need if it employed the coaches.</t>
   </si>
   <si>
-    <t xml:space="preserve">Escalation rates are simulated from the engine's own rules (evals/results/hybrid-latest.json); real rates are unmeasured (GAPS #14).</t>
+    <t xml:space="preserve">Amber-day outcomes (moved / made easy / escalated) are simulated from the engine's own rules (evals/results/hybrid-latest.json); real rates are unmeasured (GAPS #14).</t>
   </si>
   <si>
     <t xml:space="preserve">Most drivers are hypotheses; each names the telemetry event or study that will replace it (see 'Drivers' column H).</t>
@@ -187,13 +194,22 @@
     <t xml:space="preserve">Measured by event:bounds_rejected</t>
   </si>
   <si>
+    <t xml:space="preserve">minutesPerLostSession</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coach minutes to review a hard session the engine made easy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measured by event:session_downgraded</t>
+  </si>
+  <si>
     <t xml:space="preserve">minutesPerEscalation</t>
   </si>
   <si>
-    <t xml:space="preserve">Coach minutes per escalation review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">min</t>
+    <t xml:space="preserve">Coach minutes per escalation (pain flag, blocked proposal, or no safe adaptation)</t>
   </si>
   <si>
     <t xml:space="preserve">Measured by event:coach_decision</t>
@@ -430,24 +446,30 @@
     <t xml:space="preserve">Hard sessions (n)</t>
   </si>
   <si>
+    <t xml:space="preserve">Moved (kept)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Made easy (coach told)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Escalated</t>
   </si>
   <si>
-    <t xml:space="preserve">Rate</t>
-  </si>
-  <si>
     <t xml:space="preserve">Segment</t>
   </si>
   <si>
     <t xml:space="preserve">3d-doubles</t>
   </si>
   <si>
+    <t xml:space="preserve">standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3d-singles</t>
+  </si>
+  <si>
     <t xml:space="preserve">rigid</t>
   </si>
   <si>
-    <t xml:space="preserve">3d-singles</t>
-  </si>
-  <si>
     <t xml:space="preserve">4d-doubles</t>
   </si>
   <si>
@@ -457,7 +479,7 @@
     <t xml:space="preserve">5d-doubles</t>
   </si>
   <si>
-    <t xml:space="preserve">standard</t>
+    <t xml:space="preserve">flexible</t>
   </si>
   <si>
     <t xml:space="preserve">5d-singles</t>
@@ -466,9 +488,6 @@
     <t xml:space="preserve">6d-doubles</t>
   </si>
   <si>
-    <t xml:space="preserve">flexible</t>
-  </si>
-  <si>
     <t xml:space="preserve">6d-singles</t>
   </si>
   <si>
@@ -478,16 +497,28 @@
     <t xml:space="preserve">7d-singles</t>
   </si>
   <si>
-    <t xml:space="preserve">Segment escalation rate (n-weighted)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flexible: 6-7 days available, doubles OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard: 5 days with doubles, or 6-7 days without</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rigid: 3-4 fixed days</t>
+    <t xml:space="preserve">Segment (n-weighted)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kept rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Made-easy rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escalation rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flexible: doubles OK, 5-7 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard: doubles OK on 3-4 days, or 6-7 single-session days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rigid: one session a day, 3-5 days</t>
   </si>
   <si>
     <t xml:space="preserve">Per athlete-month</t>
@@ -514,7 +545,16 @@
     <t xml:space="preserve">Coach cost per hour, loaded ($)</t>
   </si>
   <si>
-    <t xml:space="preserve">Escalation rate on amber days (simulated)</t>
+    <t xml:space="preserve">Amber-day hard sessions kept by moving (simulated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amber-day hard sessions made easy (simulated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amber-day hard sessions escalated (simulated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lost sessions per athlete-month (coach reviews)</t>
   </si>
   <si>
     <t xml:space="preserve">Escalations per athlete-month</t>
@@ -883,10 +923,10 @@
     <t xml:space="preserve">OWN-002</t>
   </si>
   <si>
-    <t xml:space="preserve">Simulated amber-day escalation rate by schedule shape (share of hard sessions the engine cannot reschedule within rules H1-H9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evals/results/hybrid-latest.json, amber_escalation_by_schedule (CI). Simulation of the engine's own rules; real-world rates are unmeasured</t>
+    <t xml:space="preserve">Simulated amber-day outcomes by schedule shape: share of hard sessions the engine keeps by moving them, makes easy in place (coach told), or escalates, within rules H1-H9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evals/results/hybrid-latest.json, amber_outcomes_by_schedule (CI). Simulation of the engine's own rules; real-world rates are unmeasured</t>
   </si>
   <si>
     <t xml:space="preserve">../../evals/results/hybrid-latest.json</t>
@@ -1395,7 +1435,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -1569,14 +1609,14 @@
       <c r="B7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>8</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>37</v>
@@ -1596,42 +1636,42 @@
         <v>40</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>18</v>
@@ -1647,43 +1687,43 @@
       <c r="B10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>1.3</v>
+      <c r="C10" s="5" t="n">
+        <v>15</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.2</v>
+        <v>8</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.5</v>
+        <v>30</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>18</v>
@@ -1699,23 +1739,23 @@
       <c r="B12" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>10</v>
+      <c r="C12" s="5" t="n">
+        <v>1.5</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1726,13 +1766,13 @@
         <v>57</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2000</v>
+        <v>10</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4000</v>
+        <v>15</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>58</v>
@@ -1741,59 +1781,59 @@
         <v>18</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>600</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>24</v>
+        <v>600</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>12</v>
+        <v>300</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>60</v>
+        <v>1200</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1804,94 +1844,94 @@
         <v>66</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.5</v>
+        <v>24</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.5</v>
+        <v>60</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>67</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="H17" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>18</v>
@@ -1907,145 +1947,157 @@
       <c r="B20" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="4" t="n">
-        <v>0.03</v>
+      <c r="C20" s="5" t="n">
+        <v>8</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.02</v>
+        <v>5</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.05</v>
+        <v>12</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="4" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>24000</v>
-      </c>
-      <c r="F22" s="2" t="s">
+      <c r="G22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>24000</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="G23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
         <v>98</v>
       </c>
+      <c r="B25" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="H27" s="2" t="s">
+      <c r="A27" s="1" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2057,7 +2109,7 @@
         <v>103</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.6725</v>
+        <v>4.33</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>104</v>
@@ -2071,7 +2123,7 @@
         <v>106</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4556</v>
+        <v>3.6725</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>107</v>
@@ -2085,7 +2137,7 @@
         <v>109</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>173.33</v>
+        <v>4556</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>110</v>
@@ -2099,10 +2151,24 @@
         <v>112</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>22.67</v>
+        <v>173.33</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>113</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2121,250 +2187,313 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>1416</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1275</v>
-      </c>
-      <c r="D2" s="6" t="n">
-        <f aca="false">IFERROR(C2/B2,0)</f>
-        <v>0.900423728813559</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>120</v>
+        <v>423</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>993</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>954</v>
       </c>
       <c r="C3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>954</v>
       </c>
-      <c r="D3" s="6" t="n">
-        <f aca="false">IFERROR(C3/B3,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>120</v>
+      <c r="E3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>1458</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>876</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <f aca="false">IFERROR(C4/B4,0)</f>
-        <v>0.60082304526749</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>120</v>
+        <v>936</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>522</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>1206</v>
       </c>
       <c r="C5" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="D5" s="4" t="n">
         <v>1161</v>
       </c>
-      <c r="D5" s="6" t="n">
-        <f aca="false">IFERROR(C5/B5,0)</f>
-        <v>0.962686567164179</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>120</v>
+      <c r="E5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>1458</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>540</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <f aca="false">IFERROR(C6/B6,0)</f>
-        <v>0.37037037037037</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>125</v>
+        <v>1098</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>360</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>1368</v>
       </c>
       <c r="C7" s="4" t="n">
+        <v>156</v>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>1212</v>
       </c>
-      <c r="D7" s="6" t="n">
-        <f aca="false">IFERROR(C7/B7,0)</f>
-        <v>0.885964912280702</v>
-      </c>
-      <c r="E7" s="2"/>
+      <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>1458</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>342</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <f aca="false">IFERROR(C8/B8,0)</f>
-        <v>0.234567901234568</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>128</v>
+        <v>1152</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>306</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>1440</v>
       </c>
       <c r="C9" s="4" t="n">
+        <v>432</v>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>1008</v>
       </c>
-      <c r="D9" s="6" t="n">
-        <f aca="false">IFERROR(C9/B9,0)</f>
-        <v>0.7</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>125</v>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>1458</v>
       </c>
       <c r="C10" s="4" t="n">
+        <v>1098</v>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>360</v>
       </c>
-      <c r="D10" s="6" t="n">
-        <f aca="false">IFERROR(C10/B10,0)</f>
-        <v>0.246913580246914</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>128</v>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>1458</v>
       </c>
       <c r="C11" s="4" t="n">
+        <v>675</v>
+      </c>
+      <c r="D11" s="4" t="n">
         <v>783</v>
       </c>
-      <c r="D11" s="6" t="n">
-        <f aca="false">IFERROR(C11/B11,0)</f>
-        <v>0.537037037037037</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>132</v>
-      </c>
+      <c r="E11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <f aca="false">IFERROR(SUMIFS($C$2:$C$11,$F$2:$F$11,A14)/SUMIFS($B$2:$B$11,$F$2:$F$11,A14),0)</f>
+        <v>0.765432098765432</v>
       </c>
       <c r="D14" s="6" t="n">
-        <f aca="false">IFERROR(SUMIFS($C$2:$C$11,$E$2:$E$11,A14)/SUMIFS($B$2:$B$11,$E$2:$E$11,A14),0)</f>
-        <v>0.240740740740741</v>
+        <f aca="false">IFERROR(SUMIFS($D$2:$D$11,$F$2:$F$11,A14)/SUMIFS($B$2:$B$11,$F$2:$F$11,A14),0)</f>
+        <v>0.234567901234568</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <f aca="false">IFERROR(SUMIFS($E$2:$E$11,$F$2:$F$11,A14)/SUMIFS($B$2:$B$11,$F$2:$F$11,A14),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <f aca="false">IFERROR(SUMIFS($C$2:$C$11,$F$2:$F$11,A15)/SUMIFS($B$2:$B$11,$F$2:$F$11,A15),0)</f>
+        <v>0.427234927234927</v>
       </c>
       <c r="D15" s="6" t="n">
-        <f aca="false">IFERROR(SUMIFS($C$2:$C$11,$E$2:$E$11,A15)/SUMIFS($B$2:$B$11,$E$2:$E$11,A15),0)</f>
-        <v>0.535123966942149</v>
+        <f aca="false">IFERROR(SUMIFS($D$2:$D$11,$F$2:$F$11,A15)/SUMIFS($B$2:$B$11,$F$2:$F$11,A15),0)</f>
+        <v>0.572765072765073</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <f aca="false">IFERROR(SUMIFS($E$2:$E$11,$F$2:$F$11,A15)/SUMIFS($B$2:$B$11,$F$2:$F$11,A15),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <f aca="false">IFERROR(SUMIFS($C$2:$C$11,$F$2:$F$11,A16)/SUMIFS($B$2:$B$11,$F$2:$F$11,A16),0)</f>
+        <v>0.0569727891156463</v>
       </c>
       <c r="D16" s="6" t="n">
-        <f aca="false">IFERROR(SUMIFS($C$2:$C$11,$E$2:$E$11,A16)/SUMIFS($B$2:$B$11,$E$2:$E$11,A16),0)</f>
-        <v>0.847437425506555</v>
+        <f aca="false">IFERROR(SUMIFS($D$2:$D$11,$F$2:$F$11,A16)/SUMIFS($B$2:$B$11,$F$2:$F$11,A16),0)</f>
+        <v>0.943027210884354</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <f aca="false">IFERROR(SUMIFS($E$2:$E$11,$F$2:$F$11,A16)/SUMIFS($B$2:$B$11,$F$2:$F$11,A16),0)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2384,7 +2513,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
@@ -2393,30 +2522,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B2" s="7" t="n">
         <f aca="false">(uaeMonthlyWageAed/uaeHoursPerMonth/fxAedPerUsd)*coachLoading*specialistPremium</f>
@@ -2445,406 +2574,493 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B3" s="8" t="n">
-        <f aca="false">esc_flexible</f>
-        <v>0.240740740740741</v>
+        <f aca="false">kept_flexible</f>
+        <v>0.765432098765432</v>
       </c>
       <c r="C3" s="8" t="n">
-        <f aca="false">esc_standard</f>
-        <v>0.535123966942149</v>
+        <f aca="false">kept_standard</f>
+        <v>0.427234927234927</v>
       </c>
       <c r="D3" s="8" t="n">
-        <f aca="false">esc_rigid</f>
-        <v>0.847437425506555</v>
+        <f aca="false">kept_rigid</f>
+        <v>0.0569727891156463</v>
       </c>
       <c r="E3" s="8" t="n">
-        <f aca="false">esc_flexible</f>
-        <v>0.240740740740741</v>
+        <f aca="false">kept_flexible</f>
+        <v>0.765432098765432</v>
       </c>
       <c r="F3" s="8" t="n">
-        <f aca="false">esc_standard</f>
-        <v>0.535123966942149</v>
+        <f aca="false">kept_standard</f>
+        <v>0.427234927234927</v>
       </c>
       <c r="G3" s="8" t="n">
-        <f aca="false">esc_rigid</f>
-        <v>0.847437425506555</v>
+        <f aca="false">kept_rigid</f>
+        <v>0.0569727891156463</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B4" s="9" t="n">
-        <f aca="false">amberDaysPerAthleteMonth*hardShareOnAmber*B3+painFlagsPerAthleteMonth+llmProposalsPerAthleteMonth*proposalRejectRate</f>
-        <v>1.52727777777778</v>
-      </c>
-      <c r="C4" s="9" t="n">
-        <f aca="false">amberDaysPerAthleteMonth*hardShareOnAmber*C3+painFlagsPerAthleteMonth+llmProposalsPerAthleteMonth*proposalRejectRate</f>
-        <v>2.23379752066116</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <f aca="false">amberDaysPerAthleteMonth*hardShareOnAmber*D3+painFlagsPerAthleteMonth+llmProposalsPerAthleteMonth*proposalRejectRate</f>
-        <v>2.98334982121573</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <f aca="false">amberDaysPerAthleteMonth*hardShareOnAmber*E3+painFlagsPerAthleteMonth+llmProposalsPerAthleteMonth*proposalRejectRate</f>
-        <v>1.52727777777778</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <f aca="false">amberDaysPerAthleteMonth*hardShareOnAmber*F3+painFlagsPerAthleteMonth+llmProposalsPerAthleteMonth*proposalRejectRate</f>
-        <v>2.23379752066116</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <f aca="false">amberDaysPerAthleteMonth*hardShareOnAmber*G3+painFlagsPerAthleteMonth+llmProposalsPerAthleteMonth*proposalRejectRate</f>
-        <v>2.98334982121573</v>
+        <v>153</v>
+      </c>
+      <c r="B4" s="8" t="n">
+        <f aca="false">down_flexible</f>
+        <v>0.234567901234568</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <f aca="false">down_standard</f>
+        <v>0.572765072765073</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <f aca="false">down_rigid</f>
+        <v>0.943027210884354</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <f aca="false">down_flexible</f>
+        <v>0.234567901234568</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <f aca="false">down_standard</f>
+        <v>0.572765072765073</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <f aca="false">down_rigid</f>
+        <v>0.943027210884354</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B5" s="10" t="n">
-        <f aca="false">triageMinutesPerAthleteWeek*weeksPerMonth+B4*minutesPerEscalation</f>
-        <v>12.6041111111111</v>
-      </c>
-      <c r="C5" s="10" t="n">
-        <f aca="false">triageMinutesPerAthleteWeek*weeksPerMonth+C4*minutesPerEscalation</f>
-        <v>15.4301900826446</v>
-      </c>
-      <c r="D5" s="10" t="n">
-        <f aca="false">triageMinutesPerAthleteWeek*weeksPerMonth+D4*minutesPerEscalation</f>
-        <v>18.4283992848629</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <f aca="false">triageMinutesPerAthleteWeek*weeksPerMonth+E4*minutesPerEscalation</f>
-        <v>12.6041111111111</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <f aca="false">triageMinutesPerAthleteWeek*weeksPerMonth+F4*minutesPerEscalation</f>
-        <v>15.4301900826446</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <f aca="false">triageMinutesPerAthleteWeek*weeksPerMonth+G4*minutesPerEscalation</f>
-        <v>18.4283992848629</v>
+        <v>154</v>
+      </c>
+      <c r="B5" s="8" t="n">
+        <f aca="false">esc_flexible</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="8" t="n">
+        <f aca="false">esc_standard</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <f aca="false">esc_rigid</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <f aca="false">esc_flexible</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <f aca="false">esc_standard</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <f aca="false">esc_rigid</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="10" t="n">
+        <v>155</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <f aca="false">amberDaysPerAthleteMonth*hardShareOnAmber*B4</f>
+        <v>0.562962962962963</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <f aca="false">amberDaysPerAthleteMonth*hardShareOnAmber*C4</f>
+        <v>1.37463617463617</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <f aca="false">amberDaysPerAthleteMonth*hardShareOnAmber*D4</f>
+        <v>2.26326530612245</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <f aca="false">amberDaysPerAthleteMonth*hardShareOnAmber*E4</f>
+        <v>0.562962962962963</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <f aca="false">amberDaysPerAthleteMonth*hardShareOnAmber*F4</f>
+        <v>1.37463617463617</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <f aca="false">amberDaysPerAthleteMonth*hardShareOnAmber*G4</f>
+        <v>2.26326530612245</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <f aca="false">amberDaysPerAthleteMonth*hardShareOnAmber*B5+painFlagsPerAthleteMonth+llmProposalsPerAthleteMonth*proposalRejectRate</f>
+        <v>0.9495</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <f aca="false">amberDaysPerAthleteMonth*hardShareOnAmber*C5+painFlagsPerAthleteMonth+llmProposalsPerAthleteMonth*proposalRejectRate</f>
+        <v>0.9495</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <f aca="false">amberDaysPerAthleteMonth*hardShareOnAmber*D5+painFlagsPerAthleteMonth+llmProposalsPerAthleteMonth*proposalRejectRate</f>
+        <v>0.9495</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <f aca="false">amberDaysPerAthleteMonth*hardShareOnAmber*E5+painFlagsPerAthleteMonth+llmProposalsPerAthleteMonth*proposalRejectRate</f>
+        <v>0.9495</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <f aca="false">amberDaysPerAthleteMonth*hardShareOnAmber*F5+painFlagsPerAthleteMonth+llmProposalsPerAthleteMonth*proposalRejectRate</f>
+        <v>0.9495</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <f aca="false">amberDaysPerAthleteMonth*hardShareOnAmber*G5+painFlagsPerAthleteMonth+llmProposalsPerAthleteMonth*proposalRejectRate</f>
+        <v>0.9495</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B8" s="10" t="n">
+        <f aca="false">triageMinutesPerAthleteWeek*weeksPerMonth+B6*minutesPerLostSession+B7*minutesPerEscalation</f>
+        <v>11.1374444444444</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <f aca="false">triageMinutesPerAthleteWeek*weeksPerMonth+C6*minutesPerLostSession+C7*minutesPerEscalation</f>
+        <v>12.3549542619543</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <f aca="false">triageMinutesPerAthleteWeek*weeksPerMonth+D6*minutesPerLostSession+D7*minutesPerEscalation</f>
+        <v>13.6878979591837</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <f aca="false">triageMinutesPerAthleteWeek*weeksPerMonth+E6*minutesPerLostSession+E7*minutesPerEscalation</f>
+        <v>11.1374444444444</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <f aca="false">triageMinutesPerAthleteWeek*weeksPerMonth+F6*minutesPerLostSession+F7*minutesPerEscalation</f>
+        <v>12.3549542619543</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <f aca="false">triageMinutesPerAthleteWeek*weeksPerMonth+G6*minutesPerLostSession+G7*minutesPerEscalation</f>
+        <v>13.6878979591837</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" s="10" t="n">
         <f aca="false">manualMinutesPerAthleteWeek*weeksPerMonth</f>
         <v>64.95</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C9" s="10" t="n">
         <f aca="false">manualMinutesPerAthleteWeek*weeksPerMonth</f>
         <v>64.95</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D9" s="10" t="n">
         <f aca="false">manualMinutesPerAthleteWeek*weeksPerMonth</f>
         <v>64.95</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E9" s="10" t="n">
         <f aca="false">manualMinutesPerAthleteWeek*weeksPerMonth</f>
         <v>64.95</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F9" s="10" t="n">
         <f aca="false">manualMinutesPerAthleteWeek*weeksPerMonth</f>
         <v>64.95</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G9" s="10" t="n">
         <f aca="false">manualMinutesPerAthleteWeek*weeksPerMonth</f>
         <v>64.95</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B7" s="10" t="n">
-        <f aca="false">B6-B5</f>
-        <v>52.3458888888889</v>
-      </c>
-      <c r="C7" s="10" t="n">
-        <f aca="false">C6-C5</f>
-        <v>49.5198099173554</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <f aca="false">D6-D5</f>
-        <v>46.5216007151371</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <f aca="false">E6-E5</f>
-        <v>52.3458888888889</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <f aca="false">F6-F5</f>
-        <v>49.5198099173554</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <f aca="false">G6-G5</f>
-        <v>46.5216007151371</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B8" s="7" t="n">
-        <f aca="false">B7/60*B2</f>
-        <v>12.1762656316116</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <f aca="false">C7/60*C2</f>
-        <v>11.518886628528</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <f aca="false">D7/60*D2</f>
-        <v>10.8214681217405</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <f aca="false">E7/60*E2</f>
-        <v>38.5671422861111</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <f aca="false">F7/60*F2</f>
-        <v>36.4849579518595</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <f aca="false">G7/60*G2</f>
-        <v>34.2759523668951</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B9" s="11" t="n">
-        <f aca="false">IFERROR(B8/pricePerAthleteMonthUsd,0)</f>
-        <v>1.52203320395145</v>
-      </c>
-      <c r="C9" s="11" t="n">
-        <f aca="false">IFERROR(C8/pricePerAthleteMonthUsd,0)</f>
-        <v>1.439860828566</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <f aca="false">IFERROR(D8/pricePerAthleteMonthUsd,0)</f>
-        <v>1.35268351521756</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <f aca="false">IFERROR(E8/pricePerAthleteMonthUsd,0)</f>
-        <v>4.82089278576389</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <f aca="false">IFERROR(F8/pricePerAthleteMonthUsd,0)</f>
-        <v>4.56061974398244</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <f aca="false">IFERROR(G8/pricePerAthleteMonthUsd,0)</f>
-        <v>4.28449404586189</v>
-      </c>
-    </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B10" s="12" t="n">
-        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/B6,0)</f>
-        <v>40</v>
-      </c>
-      <c r="C10" s="12" t="n">
-        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/C6,0)</f>
-        <v>40</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/D6,0)</f>
-        <v>40</v>
-      </c>
-      <c r="E10" s="12" t="n">
-        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/E6,0)</f>
-        <v>40</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/F6,0)</f>
-        <v>40</v>
-      </c>
-      <c r="G10" s="12" t="n">
-        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/G6,0)</f>
-        <v>40</v>
+        <v>159</v>
+      </c>
+      <c r="B10" s="10" t="n">
+        <f aca="false">B9-B8</f>
+        <v>53.8125555555556</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <f aca="false">C9-C8</f>
+        <v>52.5950457380457</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <f aca="false">D9-D8</f>
+        <v>51.2621020408163</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <f aca="false">E9-E8</f>
+        <v>53.8125555555556</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <f aca="false">F9-F8</f>
+        <v>52.5950457380457</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <f aca="false">G9-G8</f>
+        <v>51.2621020408163</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B11" s="12" t="n">
-        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/B5,0)</f>
-        <v>206.123222581697</v>
-      </c>
-      <c r="C11" s="12" t="n">
-        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/C5,0)</f>
-        <v>168.371224598338</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/D5,0)</f>
-        <v>140.978061080649</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/E5,0)</f>
-        <v>206.123222581697</v>
-      </c>
-      <c r="F11" s="12" t="n">
-        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/F5,0)</f>
-        <v>168.371224598338</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/G5,0)</f>
-        <v>140.978061080649</v>
+        <v>160</v>
+      </c>
+      <c r="B11" s="7" t="n">
+        <f aca="false">B10/60*B2</f>
+        <v>12.5174294422839</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <f aca="false">C10/60*C2</f>
+        <v>12.2342224271435</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <f aca="false">D10/60*D2</f>
+        <v>11.9241641422627</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <f aca="false">E10/60*E2</f>
+        <v>39.6477456194445</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <f aca="false">F10/60*F2</f>
+        <v>38.7507148236487</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <f aca="false">G10/60*G2</f>
+        <v>37.7686352311225</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B12" s="7" t="n">
+        <v>161</v>
+      </c>
+      <c r="B12" s="11" t="n">
+        <f aca="false">IFERROR(B11/pricePerAthleteMonthUsd,0)</f>
+        <v>1.56467868028549</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <f aca="false">IFERROR(C11/pricePerAthleteMonthUsd,0)</f>
+        <v>1.52927780339294</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <f aca="false">IFERROR(D11/pricePerAthleteMonthUsd,0)</f>
+        <v>1.49052051778284</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <f aca="false">IFERROR(E11/pricePerAthleteMonthUsd,0)</f>
+        <v>4.95596820243056</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <f aca="false">IFERROR(F11/pricePerAthleteMonthUsd,0)</f>
+        <v>4.84383935295608</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <f aca="false">IFERROR(G11/pricePerAthleteMonthUsd,0)</f>
+        <v>4.72107940389031</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B13" s="12" t="n">
+        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/B9,0)</f>
+        <v>40</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/C9,0)</f>
+        <v>40</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/D9,0)</f>
+        <v>40</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/E9,0)</f>
+        <v>40</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/F9,0)</f>
+        <v>40</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/G9,0)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B14" s="12" t="n">
+        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/B8,0)</f>
+        <v>233.267156838293</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/C8,0)</f>
+        <v>210.280017628253</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/D8,0)</f>
+        <v>189.802700732212</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/E8,0)</f>
+        <v>233.267156838293</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/F8,0)</f>
+        <v>210.280017628253</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <f aca="false">IFERROR(coachProgrammingHoursPerWeek*60*weeksPerMonth/G8,0)</f>
+        <v>189.802700732212</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B15" s="7" t="n">
         <f aca="false">llmCallsPerAthleteMonth*(llmTokensInPerProposal*priceInPer1M+llmTokensOutPerProposal*priceOutPer1M)/1000000</f>
         <v>0.2016</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C15" s="7" t="n">
         <f aca="false">llmCallsPerAthleteMonth*(llmTokensInPerProposal*priceInPer1M+llmTokensOutPerProposal*priceOutPer1M)/1000000</f>
         <v>0.2016</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D15" s="7" t="n">
         <f aca="false">llmCallsPerAthleteMonth*(llmTokensInPerProposal*priceInPer1M+llmTokensOutPerProposal*priceOutPer1M)/1000000</f>
         <v>0.2016</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E15" s="7" t="n">
         <f aca="false">llmCallsPerAthleteMonth*(llmTokensInPerProposal*priceInPer1M+llmTokensOutPerProposal*priceOutPer1M)/1000000</f>
         <v>0.2016</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F15" s="7" t="n">
         <f aca="false">llmCallsPerAthleteMonth*(llmTokensInPerProposal*priceInPer1M+llmTokensOutPerProposal*priceOutPer1M)/1000000</f>
         <v>0.2016</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G15" s="7" t="n">
         <f aca="false">llmCallsPerAthleteMonth*(llmTokensInPerProposal*priceInPer1M+llmTokensOutPerProposal*priceOutPer1M)/1000000</f>
         <v>0.2016</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B13" s="6" t="n">
-        <f aca="false">IFERROR(1-(B12+infraPerAthleteMonthUsd+pricePerAthleteMonthUsd*paymentFeeRate)/pricePerAthleteMonthUsd,0)</f>
-        <v>0.92605</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <f aca="false">IFERROR(1-(C12+infraPerAthleteMonthUsd+pricePerAthleteMonthUsd*paymentFeeRate)/pricePerAthleteMonthUsd,0)</f>
-        <v>0.92605</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <f aca="false">IFERROR(1-(D12+infraPerAthleteMonthUsd+pricePerAthleteMonthUsd*paymentFeeRate)/pricePerAthleteMonthUsd,0)</f>
-        <v>0.92605</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <f aca="false">IFERROR(1-(E12+infraPerAthleteMonthUsd+pricePerAthleteMonthUsd*paymentFeeRate)/pricePerAthleteMonthUsd,0)</f>
-        <v>0.92605</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <f aca="false">IFERROR(1-(F12+infraPerAthleteMonthUsd+pricePerAthleteMonthUsd*paymentFeeRate)/pricePerAthleteMonthUsd,0)</f>
-        <v>0.92605</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <f aca="false">IFERROR(1-(G12+infraPerAthleteMonthUsd+pricePerAthleteMonthUsd*paymentFeeRate)/pricePerAthleteMonthUsd,0)</f>
-        <v>0.92605</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B14" s="7" t="n">
-        <f aca="false">B5/60*B2</f>
-        <v>2.93186357509371</v>
-      </c>
-      <c r="C14" s="7" t="n">
-        <f aca="false">C5/60*C2</f>
-        <v>3.58924257817733</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <f aca="false">D5/60*D2</f>
-        <v>4.28666108496482</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <f aca="false">E5/60*E2</f>
-        <v>9.28639396388889</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <f aca="false">F5/60*F2</f>
-        <v>11.3685782981405</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <f aca="false">G5/60*G2</f>
-        <v>13.5775838831049</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B15" s="7" t="n">
-        <f aca="false">IFERROR((B14+B12+infraPerAthleteMonthUsd)/(1-targetGrossMargin-paymentFeeRate),0)</f>
-        <v>12.1609762040508</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <f aca="false">IFERROR((C14+C12+infraPerAthleteMonthUsd)/(1-targetGrossMargin-paymentFeeRate),0)</f>
-        <v>14.5957132525086</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <f aca="false">IFERROR((D14+D12+infraPerAthleteMonthUsd)/(1-targetGrossMargin-paymentFeeRate),0)</f>
-        <v>17.1787447591289</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <f aca="false">IFERROR((E14+E12+infraPerAthleteMonthUsd)/(1-targetGrossMargin-paymentFeeRate),0)</f>
-        <v>35.6962739403292</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <f aca="false">IFERROR((F14+F12+infraPerAthleteMonthUsd)/(1-targetGrossMargin-paymentFeeRate),0)</f>
-        <v>43.4080677708907</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <f aca="false">IFERROR((G14+G12+infraPerAthleteMonthUsd)/(1-targetGrossMargin-paymentFeeRate),0)</f>
-        <v>51.5895699374255</v>
-      </c>
-    </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B16" s="13" t="n">
+        <v>165</v>
+      </c>
+      <c r="B16" s="6" t="n">
+        <f aca="false">IFERROR(1-(B15+infraPerAthleteMonthUsd+pricePerAthleteMonthUsd*paymentFeeRate)/pricePerAthleteMonthUsd,0)</f>
+        <v>0.92605</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <f aca="false">IFERROR(1-(C15+infraPerAthleteMonthUsd+pricePerAthleteMonthUsd*paymentFeeRate)/pricePerAthleteMonthUsd,0)</f>
+        <v>0.92605</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <f aca="false">IFERROR(1-(D15+infraPerAthleteMonthUsd+pricePerAthleteMonthUsd*paymentFeeRate)/pricePerAthleteMonthUsd,0)</f>
+        <v>0.92605</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <f aca="false">IFERROR(1-(E15+infraPerAthleteMonthUsd+pricePerAthleteMonthUsd*paymentFeeRate)/pricePerAthleteMonthUsd,0)</f>
+        <v>0.92605</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <f aca="false">IFERROR(1-(F15+infraPerAthleteMonthUsd+pricePerAthleteMonthUsd*paymentFeeRate)/pricePerAthleteMonthUsd,0)</f>
+        <v>0.92605</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <f aca="false">IFERROR(1-(G15+infraPerAthleteMonthUsd+pricePerAthleteMonthUsd*paymentFeeRate)/pricePerAthleteMonthUsd,0)</f>
+        <v>0.92605</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B17" s="7" t="n">
+        <f aca="false">B8/60*B2</f>
+        <v>2.59069976442138</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <f aca="false">C8/60*C2</f>
+        <v>2.87390677956181</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <f aca="false">D8/60*D2</f>
+        <v>3.18396506444257</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <f aca="false">E8/60*E2</f>
+        <v>8.20579063055556</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <f aca="false">F8/60*F2</f>
+        <v>9.10282142635135</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <f aca="false">G8/60*G2</f>
+        <v>10.0849010188776</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B18" s="7" t="n">
+        <f aca="false">IFERROR((B17+B15+infraPerAthleteMonthUsd)/(1-targetGrossMargin-paymentFeeRate),0)</f>
+        <v>10.897406534894</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <f aca="false">IFERROR((C17+C15+infraPerAthleteMonthUsd)/(1-targetGrossMargin-paymentFeeRate),0)</f>
+        <v>11.9463214057845</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <f aca="false">IFERROR((D17+D15+infraPerAthleteMonthUsd)/(1-targetGrossMargin-paymentFeeRate),0)</f>
+        <v>13.0946854238614</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <f aca="false">IFERROR((E17+E15+infraPerAthleteMonthUsd)/(1-targetGrossMargin-paymentFeeRate),0)</f>
+        <v>31.694039372428</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <f aca="false">IFERROR((F17+F15+infraPerAthleteMonthUsd)/(1-targetGrossMargin-paymentFeeRate),0)</f>
+        <v>35.0163756531532</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <f aca="false">IFERROR((G17+G15+infraPerAthleteMonthUsd)/(1-targetGrossMargin-paymentFeeRate),0)</f>
+        <v>38.6537074773243</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B19" s="13" t="n">
         <f aca="false">pricePerAthleteMonthUsd*fxAedPerUsd</f>
         <v>29.38</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C19" s="13" t="n">
         <f aca="false">pricePerAthleteMonthUsd*fxAedPerUsd</f>
         <v>29.38</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D19" s="13" t="n">
         <f aca="false">pricePerAthleteMonthUsd*fxAedPerUsd</f>
         <v>29.38</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E19" s="13" t="n">
         <f aca="false">pricePerAthleteMonthUsd*fxAedPerUsd</f>
         <v>29.38</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F19" s="13" t="n">
         <f aca="false">pricePerAthleteMonthUsd*fxAedPerUsd</f>
         <v>29.38</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="G19" s="13" t="n">
         <f aca="false">pricePerAthleteMonthUsd*fxAedPerUsd</f>
         <v>29.38</v>
       </c>
@@ -2874,15 +3090,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B2" s="14" t="n">
         <f aca="false">arrTargetUsd</f>
@@ -2891,7 +3107,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="B3" s="13" t="n">
         <f aca="false">IFERROR(arrTargetUsd/(12*pricePerAthleteMonthUsd),0)</f>
@@ -2900,7 +3116,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="B4" s="13" t="n">
         <f aca="false">IFERROR(B3/athletesPerClub,0)</f>
@@ -2909,7 +3125,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B5" s="6" t="n">
         <f aca="false">IFERROR(B4/hyroxGyms,0)</f>
@@ -2947,539 +3163,539 @@
         <v>7</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
